--- a/XD4/Đoạn 2/4. K98 Base - XD4 đoạn 2.xlsx
+++ b/XD4/Đoạn 2/4. K98 Base - XD4 đoạn 2.xlsx
@@ -160,7 +160,7 @@
     <t xml:space="preserve">Nguyễn Xuân Hưng</t>
   </si>
   <si>
-    <t xml:space="preserve">Trần Mạnh Tùng</t>
+    <t xml:space="preserve">Lê Quốc Huy</t>
   </si>
   <si>
     <t xml:space="preserve">PHỤ LỤC KHỐI LƯỢNG </t>
